--- a/data/excel/items.xlsx
+++ b/data/excel/items.xlsx
@@ -65,11 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -442,16 +443,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -487,357 +488,321 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>攻击力</t>
+          <t>回复量</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>防御力</t>
+          <t>stats_attack</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>最大生命</t>
+          <t>stats_defense</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>移动速度</t>
+          <t>stats_max_hp</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>回复量</t>
+          <t>stats_move_speed</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1001</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>铁剑</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>weapon</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>一把普通的铁剑</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n">
+      <c r="E2" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>1002</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>铁甲</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>armor</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>一件普通的铁甲</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n">
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2" t="n">
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="J3" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="J3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="K3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>1003</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>铁靴</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>boots</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>一双普通的铁靴</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n">
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="n">
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="n">
         <v>10</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>1004</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>生命戒指</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>accessory</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>增加少量生命值</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="n">
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2" t="n">
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="J5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="K5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>回复药水</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>consumable</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>恢复30点生命值</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="G6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="2" t="n">
+      <c r="G6" s="3" t="n">
         <v>30</v>
       </c>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>解毒草</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>consumable</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>解除中毒状态</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="G7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>3001</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>木材</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>material</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>基础材料</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="3" t="n">
         <v>999</v>
       </c>
-      <c r="G8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>3002</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>铁矿石</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>material</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>基础材料</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="3" t="n">
         <v>999</v>
       </c>
-      <c r="G9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K9"/>
